--- a/MSPS/MSPS_Producto.xlsx
+++ b/MSPS/MSPS_Producto.xlsx
@@ -2801,13 +2801,13 @@
         <v>0.1087724154525642</v>
       </c>
       <c r="L2" s="2">
-        <v>112.2262160580291</v>
+        <v>111.9612147751073</v>
       </c>
       <c r="M2" s="2">
-        <v>0.3937779547655862</v>
+        <v>0.3928481215513465</v>
       </c>
       <c r="N2" s="2">
-        <v>0.1220711659773317</v>
+        <v>0.1217829176809174</v>
       </c>
     </row>
     <row r="3" spans="1:14">
